--- a/agents/agent_profiles.xlsx
+++ b/agents/agent_profiles.xlsx
@@ -1339,7 +1339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF249"/>
+  <dimension ref="A1:AH249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1503,6 +1503,16 @@
           <t>revenue_monthly_target</t>
         </is>
       </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>owners</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>occupation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1535,7 +1545,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>KKqlLyGM</t>
+          <t>MSNLUS31</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -1577,6 +1587,8 @@
         </is>
       </c>
       <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1609,7 +1621,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>yMxruLqs</t>
+          <t>WFQDUS22</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -1651,6 +1663,8 @@
         </is>
       </c>
       <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1683,7 +1697,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>pLATCDye</t>
+          <t>BOPLUS44</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1725,6 +1739,8 @@
         </is>
       </c>
       <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1808,7 +1824,7 @@
         </is>
       </c>
       <c r="U5" t="n">
-        <v>690.34</v>
+        <v>24937.5</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
@@ -1835,8 +1851,10 @@
         </is>
       </c>
       <c r="AF5" t="n">
-        <v>39.47</v>
-      </c>
+        <v>6.68</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1916,7 +1934,7 @@
         </is>
       </c>
       <c r="U6" t="n">
-        <v>2242.09</v>
+        <v>119312.25</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
@@ -1943,8 +1961,10 @@
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>31</v>
-      </c>
+        <v>2.79</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2024,7 +2044,7 @@
         </is>
       </c>
       <c r="U7" t="n">
-        <v>393.23</v>
+        <v>20231.5</v>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
@@ -2051,8 +2071,14 @@
         </is>
       </c>
       <c r="AF7" t="n">
-        <v>32.19</v>
-      </c>
+        <v>2.88</v>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>PERS1014:100</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2136,7 +2162,7 @@
         </is>
       </c>
       <c r="U8" t="n">
-        <v>1274.03</v>
+        <v>24937.5</v>
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
@@ -2163,8 +2189,10 @@
         </is>
       </c>
       <c r="AF8" t="n">
-        <v>43.81</v>
-      </c>
+        <v>10.03</v>
+      </c>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2244,7 +2272,7 @@
         </is>
       </c>
       <c r="U9" t="n">
-        <v>4219.27</v>
+        <v>119312.25</v>
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
@@ -2271,8 +2299,10 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>77.98999999999999</v>
-      </c>
+        <v>5.59</v>
+      </c>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2356,7 +2386,7 @@
         </is>
       </c>
       <c r="U10" t="n">
-        <v>712.88</v>
+        <v>24937.5</v>
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
@@ -2383,8 +2413,10 @@
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>48.06</v>
-      </c>
+        <v>6.68</v>
+      </c>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2468,7 +2500,7 @@
         </is>
       </c>
       <c r="U11" t="n">
-        <v>343.05</v>
+        <v>24937.5</v>
       </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
@@ -2495,8 +2527,10 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>35.67</v>
-      </c>
+        <v>6.68</v>
+      </c>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2580,7 +2614,7 @@
         </is>
       </c>
       <c r="U12" t="n">
-        <v>4507.97</v>
+        <v>119312.25</v>
       </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
@@ -2607,8 +2641,10 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>87.33</v>
-      </c>
+        <v>6.98</v>
+      </c>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2692,7 +2728,7 @@
         </is>
       </c>
       <c r="U13" t="n">
-        <v>1575.06</v>
+        <v>9246.25</v>
       </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
@@ -2719,8 +2755,14 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>42.71</v>
-      </c>
+        <v>9.460000000000001</v>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>PERS1015:100</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2804,7 +2846,7 @@
         </is>
       </c>
       <c r="U14" t="n">
-        <v>939.86</v>
+        <v>6112.5</v>
       </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
@@ -2831,8 +2873,10 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>43.19</v>
-      </c>
+        <v>20.45</v>
+      </c>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2912,7 +2956,7 @@
         </is>
       </c>
       <c r="U15" t="n">
-        <v>495.71</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
@@ -2939,8 +2983,14 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>24.87</v>
-      </c>
+        <v>330.35</v>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>PERS1003:100</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3024,7 +3074,7 @@
         </is>
       </c>
       <c r="U16" t="n">
-        <v>335.65</v>
+        <v>32.3</v>
       </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
@@ -3051,8 +3101,14 @@
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>38.69</v>
-      </c>
+        <v>1676.73</v>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>PERS1005:100</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3136,7 +3192,7 @@
         </is>
       </c>
       <c r="U17" t="n">
-        <v>539.1</v>
+        <v>32.3</v>
       </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
@@ -3163,8 +3219,14 @@
         </is>
       </c>
       <c r="AF17" t="n">
-        <v>28.71</v>
-      </c>
+        <v>1676.73</v>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>PERS1022:100</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3248,7 +3310,7 @@
         </is>
       </c>
       <c r="U18" t="n">
-        <v>1233.01</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
@@ -3275,8 +3337,14 @@
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>45.18</v>
-      </c>
+        <v>991.05</v>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>PERS1001:100</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3360,7 +3428,7 @@
         </is>
       </c>
       <c r="U19" t="n">
-        <v>321.83</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
@@ -3387,8 +3455,14 @@
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>41.8</v>
-      </c>
+        <v>660.7</v>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>PERS1009:100</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3472,7 +3546,7 @@
         </is>
       </c>
       <c r="U20" t="n">
-        <v>321.28</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
@@ -3499,8 +3573,14 @@
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>24.27</v>
-      </c>
+        <v>660.7</v>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>PERS1018:50,PERS1020:50</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3584,7 +3664,7 @@
         </is>
       </c>
       <c r="U21" t="n">
-        <v>648.17</v>
+        <v>1766.5</v>
       </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
@@ -3611,8 +3691,14 @@
         </is>
       </c>
       <c r="AF21" t="n">
-        <v>31.84</v>
-      </c>
+        <v>14.15</v>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>PERS1019:100</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3696,7 +3782,7 @@
         </is>
       </c>
       <c r="U22" t="n">
-        <v>529.24</v>
+        <v>1766.5</v>
       </c>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
@@ -3723,8 +3809,14 @@
         </is>
       </c>
       <c r="AF22" t="n">
-        <v>28.69</v>
-      </c>
+        <v>14.15</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>PERS1004:50,PERS1011:50</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3808,7 +3900,7 @@
         </is>
       </c>
       <c r="U23" t="n">
-        <v>1400.86</v>
+        <v>50462.5</v>
       </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
@@ -3835,8 +3927,10 @@
         </is>
       </c>
       <c r="AF23" t="n">
-        <v>24.54</v>
-      </c>
+        <v>2.48</v>
+      </c>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3920,7 +4014,7 @@
         </is>
       </c>
       <c r="U24" t="n">
-        <v>1239.16</v>
+        <v>50222.5</v>
       </c>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
@@ -3947,8 +4041,10 @@
         </is>
       </c>
       <c r="AF24" t="n">
-        <v>38.36</v>
-      </c>
+        <v>1.99</v>
+      </c>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4028,7 +4124,7 @@
         </is>
       </c>
       <c r="U25" t="n">
-        <v>1081.41</v>
+        <v>50222.5</v>
       </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
@@ -4055,8 +4151,10 @@
         </is>
       </c>
       <c r="AF25" t="n">
-        <v>25.91</v>
-      </c>
+        <v>1.99</v>
+      </c>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4140,7 +4238,7 @@
         </is>
       </c>
       <c r="U26" t="n">
-        <v>971.49</v>
+        <v>2946.25</v>
       </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
@@ -4167,8 +4265,14 @@
         </is>
       </c>
       <c r="AF26" t="n">
-        <v>25.21</v>
-      </c>
+        <v>14.85</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>PERS1007:100</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4252,7 +4356,7 @@
         </is>
       </c>
       <c r="U27" t="n">
-        <v>311.49</v>
+        <v>64.28</v>
       </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
@@ -4279,8 +4383,14 @@
         </is>
       </c>
       <c r="AF27" t="n">
-        <v>25.56</v>
-      </c>
+        <v>388.95</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>PERS1002:100</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4365,6 +4475,8 @@
         </is>
       </c>
       <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4449,6 +4561,8 @@
         </is>
       </c>
       <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4533,6 +4647,8 @@
         </is>
       </c>
       <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4577,7 +4693,7 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>789955841</v>
+        <v>800252842</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
@@ -4617,6 +4733,8 @@
         </is>
       </c>
       <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4701,6 +4819,8 @@
         </is>
       </c>
       <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4785,6 +4905,8 @@
         </is>
       </c>
       <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4869,6 +4991,8 @@
         </is>
       </c>
       <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4913,7 +5037,7 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>472561003</v>
+        <v>826809858</v>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
@@ -4953,6 +5077,8 @@
         </is>
       </c>
       <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4997,7 +5123,7 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>505079988</v>
+        <v>791109159</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
@@ -5037,6 +5163,8 @@
         </is>
       </c>
       <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5081,7 +5209,7 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>591219077</v>
+        <v>727766843</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
@@ -5121,6 +5249,8 @@
         </is>
       </c>
       <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5205,6 +5335,8 @@
         </is>
       </c>
       <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5249,7 +5381,7 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>112337453</v>
+        <v>921812059</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
@@ -5289,6 +5421,8 @@
         </is>
       </c>
       <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5333,7 +5467,7 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>355955848</v>
+        <v>431076620</v>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
@@ -5373,6 +5507,8 @@
         </is>
       </c>
       <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5417,7 +5553,7 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>135383517</v>
+        <v>250682333</v>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
@@ -5457,6 +5593,8 @@
         </is>
       </c>
       <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5501,7 +5639,7 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>136069862</v>
+        <v>329387558</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
@@ -5541,6 +5679,8 @@
         </is>
       </c>
       <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5625,6 +5765,8 @@
         </is>
       </c>
       <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5669,7 +5811,7 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>494828429</v>
+        <v>684094755</v>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
@@ -5709,6 +5851,8 @@
         </is>
       </c>
       <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5753,7 +5897,7 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>934072016</v>
+        <v>988800174</v>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
@@ -5793,6 +5937,8 @@
         </is>
       </c>
       <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5837,7 +5983,7 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>452165939</v>
+        <v>262399512</v>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
@@ -5877,6 +6023,8 @@
         </is>
       </c>
       <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5921,7 +6069,7 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>405607913</v>
+        <v>514526679</v>
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
@@ -5961,6 +6109,8 @@
         </is>
       </c>
       <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6045,6 +6195,8 @@
         </is>
       </c>
       <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6129,6 +6281,8 @@
         </is>
       </c>
       <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6213,6 +6367,8 @@
         </is>
       </c>
       <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6297,6 +6453,8 @@
         </is>
       </c>
       <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6381,6 +6539,8 @@
         </is>
       </c>
       <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6465,6 +6625,8 @@
         </is>
       </c>
       <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6549,6 +6711,8 @@
         </is>
       </c>
       <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6633,6 +6797,8 @@
         </is>
       </c>
       <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6717,6 +6883,8 @@
         </is>
       </c>
       <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6801,6 +6969,8 @@
         </is>
       </c>
       <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="inlineStr"/>
+      <c r="AH57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6885,6 +7055,8 @@
         </is>
       </c>
       <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="inlineStr"/>
+      <c r="AH58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6969,6 +7141,8 @@
         </is>
       </c>
       <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="inlineStr"/>
+      <c r="AH59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7053,6 +7227,8 @@
         </is>
       </c>
       <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="inlineStr"/>
+      <c r="AH60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7137,6 +7313,8 @@
         </is>
       </c>
       <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7221,6 +7399,8 @@
         </is>
       </c>
       <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7305,6 +7485,8 @@
         </is>
       </c>
       <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="inlineStr"/>
+      <c r="AH63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7389,6 +7571,8 @@
         </is>
       </c>
       <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="inlineStr"/>
+      <c r="AH64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7473,6 +7657,8 @@
         </is>
       </c>
       <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="inlineStr"/>
+      <c r="AH65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7557,6 +7743,8 @@
         </is>
       </c>
       <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="inlineStr"/>
+      <c r="AH66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7641,6 +7829,8 @@
         </is>
       </c>
       <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="inlineStr"/>
+      <c r="AH67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7725,6 +7915,8 @@
         </is>
       </c>
       <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="inlineStr"/>
+      <c r="AH68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7809,6 +8001,8 @@
         </is>
       </c>
       <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="inlineStr"/>
+      <c r="AH69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7893,6 +8087,8 @@
         </is>
       </c>
       <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="inlineStr"/>
+      <c r="AH70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7977,6 +8173,8 @@
         </is>
       </c>
       <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="inlineStr"/>
+      <c r="AH71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8061,6 +8259,8 @@
         </is>
       </c>
       <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="inlineStr"/>
+      <c r="AH72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8145,6 +8345,8 @@
         </is>
       </c>
       <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="inlineStr"/>
+      <c r="AH73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8229,6 +8431,8 @@
         </is>
       </c>
       <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="inlineStr"/>
+      <c r="AH74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8313,6 +8517,8 @@
         </is>
       </c>
       <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="inlineStr"/>
+      <c r="AH75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8397,6 +8603,8 @@
         </is>
       </c>
       <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="inlineStr"/>
+      <c r="AH76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8481,6 +8689,8 @@
         </is>
       </c>
       <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="inlineStr"/>
+      <c r="AH77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8565,6 +8775,8 @@
         </is>
       </c>
       <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="inlineStr"/>
+      <c r="AH78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8649,6 +8861,8 @@
         </is>
       </c>
       <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="inlineStr"/>
+      <c r="AH79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8733,6 +8947,8 @@
         </is>
       </c>
       <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr"/>
+      <c r="AH80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8817,6 +9033,8 @@
         </is>
       </c>
       <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="inlineStr"/>
+      <c r="AH81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8901,6 +9119,8 @@
         </is>
       </c>
       <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="inlineStr"/>
+      <c r="AH82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8985,6 +9205,8 @@
         </is>
       </c>
       <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="inlineStr"/>
+      <c r="AH83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -9069,6 +9291,8 @@
         </is>
       </c>
       <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="inlineStr"/>
+      <c r="AH84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -9153,6 +9377,8 @@
         </is>
       </c>
       <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="inlineStr"/>
+      <c r="AH85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9237,6 +9463,8 @@
         </is>
       </c>
       <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="inlineStr"/>
+      <c r="AH86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9321,6 +9549,8 @@
         </is>
       </c>
       <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="inlineStr"/>
+      <c r="AH87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9405,6 +9635,8 @@
         </is>
       </c>
       <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="inlineStr"/>
+      <c r="AH88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9489,6 +9721,8 @@
         </is>
       </c>
       <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="inlineStr"/>
+      <c r="AH89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9573,6 +9807,8 @@
         </is>
       </c>
       <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="inlineStr"/>
+      <c r="AH90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9657,6 +9893,8 @@
         </is>
       </c>
       <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="inlineStr"/>
+      <c r="AH91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9741,6 +9979,8 @@
         </is>
       </c>
       <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="inlineStr"/>
+      <c r="AH92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9825,6 +10065,8 @@
         </is>
       </c>
       <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="inlineStr"/>
+      <c r="AH93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9869,7 +10111,7 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>898431335</v>
+        <v>181662102</v>
       </c>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
@@ -9909,6 +10151,8 @@
         </is>
       </c>
       <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="inlineStr"/>
+      <c r="AH94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9993,6 +10237,8 @@
         </is>
       </c>
       <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="inlineStr"/>
+      <c r="AH95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -10077,6 +10323,8 @@
         </is>
       </c>
       <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="inlineStr"/>
+      <c r="AH96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -10161,6 +10409,8 @@
         </is>
       </c>
       <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="inlineStr"/>
+      <c r="AH97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -10245,6 +10495,8 @@
         </is>
       </c>
       <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="inlineStr"/>
+      <c r="AH98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -10329,6 +10581,8 @@
         </is>
       </c>
       <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="inlineStr"/>
+      <c r="AH99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -10413,6 +10667,8 @@
         </is>
       </c>
       <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="inlineStr"/>
+      <c r="AH100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -10457,7 +10713,7 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>658490210</v>
+        <v>471468821</v>
       </c>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr"/>
@@ -10497,6 +10753,8 @@
         </is>
       </c>
       <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="inlineStr"/>
+      <c r="AH101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10581,6 +10839,8 @@
         </is>
       </c>
       <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="inlineStr"/>
+      <c r="AH102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -10625,7 +10885,7 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>537727022</v>
+        <v>781318297</v>
       </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr"/>
@@ -10665,6 +10925,8 @@
         </is>
       </c>
       <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="inlineStr"/>
+      <c r="AH103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -10749,6 +11011,8 @@
         </is>
       </c>
       <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="inlineStr"/>
+      <c r="AH104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -10833,6 +11097,8 @@
         </is>
       </c>
       <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="inlineStr"/>
+      <c r="AH105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -10917,6 +11183,8 @@
         </is>
       </c>
       <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="inlineStr"/>
+      <c r="AH106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -11001,6 +11269,8 @@
         </is>
       </c>
       <c r="AF107" t="inlineStr"/>
+      <c r="AG107" t="inlineStr"/>
+      <c r="AH107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -11085,6 +11355,8 @@
         </is>
       </c>
       <c r="AF108" t="inlineStr"/>
+      <c r="AG108" t="inlineStr"/>
+      <c r="AH108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -11169,6 +11441,8 @@
         </is>
       </c>
       <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="inlineStr"/>
+      <c r="AH109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -11253,6 +11527,8 @@
         </is>
       </c>
       <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="inlineStr"/>
+      <c r="AH110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -11337,6 +11613,8 @@
         </is>
       </c>
       <c r="AF111" t="inlineStr"/>
+      <c r="AG111" t="inlineStr"/>
+      <c r="AH111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -11421,6 +11699,8 @@
         </is>
       </c>
       <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="inlineStr"/>
+      <c r="AH112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -11505,6 +11785,8 @@
         </is>
       </c>
       <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="inlineStr"/>
+      <c r="AH113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -11589,6 +11871,8 @@
         </is>
       </c>
       <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="inlineStr"/>
+      <c r="AH114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -11673,6 +11957,8 @@
         </is>
       </c>
       <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="inlineStr"/>
+      <c r="AH115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -11757,6 +12043,8 @@
         </is>
       </c>
       <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="inlineStr"/>
+      <c r="AH116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -11841,6 +12129,8 @@
         </is>
       </c>
       <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="inlineStr"/>
+      <c r="AH117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -11925,6 +12215,8 @@
         </is>
       </c>
       <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="inlineStr"/>
+      <c r="AH118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -12009,6 +12301,8 @@
         </is>
       </c>
       <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="inlineStr"/>
+      <c r="AH119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -12093,6 +12387,8 @@
         </is>
       </c>
       <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="inlineStr"/>
+      <c r="AH120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -12177,6 +12473,8 @@
         </is>
       </c>
       <c r="AF121" t="inlineStr"/>
+      <c r="AG121" t="inlineStr"/>
+      <c r="AH121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -12261,6 +12559,8 @@
         </is>
       </c>
       <c r="AF122" t="inlineStr"/>
+      <c r="AG122" t="inlineStr"/>
+      <c r="AH122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -12345,6 +12645,8 @@
         </is>
       </c>
       <c r="AF123" t="inlineStr"/>
+      <c r="AG123" t="inlineStr"/>
+      <c r="AH123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -12429,6 +12731,8 @@
         </is>
       </c>
       <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="inlineStr"/>
+      <c r="AH124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -12513,6 +12817,8 @@
         </is>
       </c>
       <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="inlineStr"/>
+      <c r="AH125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -12597,6 +12903,8 @@
         </is>
       </c>
       <c r="AF126" t="inlineStr"/>
+      <c r="AG126" t="inlineStr"/>
+      <c r="AH126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -12681,6 +12989,8 @@
         </is>
       </c>
       <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="inlineStr"/>
+      <c r="AH127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -12765,6 +13075,8 @@
         </is>
       </c>
       <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="inlineStr"/>
+      <c r="AH128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -12809,7 +13121,7 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>365150430</v>
+        <v>907985907</v>
       </c>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr"/>
@@ -12849,6 +13161,8 @@
         </is>
       </c>
       <c r="AF129" t="inlineStr"/>
+      <c r="AG129" t="inlineStr"/>
+      <c r="AH129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -12933,6 +13247,8 @@
         </is>
       </c>
       <c r="AF130" t="inlineStr"/>
+      <c r="AG130" t="inlineStr"/>
+      <c r="AH130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -13017,6 +13333,8 @@
         </is>
       </c>
       <c r="AF131" t="inlineStr"/>
+      <c r="AG131" t="inlineStr"/>
+      <c r="AH131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -13101,6 +13419,8 @@
         </is>
       </c>
       <c r="AF132" t="inlineStr"/>
+      <c r="AG132" t="inlineStr"/>
+      <c r="AH132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -13185,6 +13505,8 @@
         </is>
       </c>
       <c r="AF133" t="inlineStr"/>
+      <c r="AG133" t="inlineStr"/>
+      <c r="AH133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -13269,6 +13591,8 @@
         </is>
       </c>
       <c r="AF134" t="inlineStr"/>
+      <c r="AG134" t="inlineStr"/>
+      <c r="AH134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -13353,6 +13677,8 @@
         </is>
       </c>
       <c r="AF135" t="inlineStr"/>
+      <c r="AG135" t="inlineStr"/>
+      <c r="AH135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -13437,6 +13763,8 @@
         </is>
       </c>
       <c r="AF136" t="inlineStr"/>
+      <c r="AG136" t="inlineStr"/>
+      <c r="AH136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -13521,6 +13849,8 @@
         </is>
       </c>
       <c r="AF137" t="inlineStr"/>
+      <c r="AG137" t="inlineStr"/>
+      <c r="AH137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -13605,6 +13935,8 @@
         </is>
       </c>
       <c r="AF138" t="inlineStr"/>
+      <c r="AG138" t="inlineStr"/>
+      <c r="AH138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -13689,6 +14021,8 @@
         </is>
       </c>
       <c r="AF139" t="inlineStr"/>
+      <c r="AG139" t="inlineStr"/>
+      <c r="AH139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -13773,6 +14107,8 @@
         </is>
       </c>
       <c r="AF140" t="inlineStr"/>
+      <c r="AG140" t="inlineStr"/>
+      <c r="AH140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -13857,6 +14193,8 @@
         </is>
       </c>
       <c r="AF141" t="inlineStr"/>
+      <c r="AG141" t="inlineStr"/>
+      <c r="AH141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -13941,6 +14279,8 @@
         </is>
       </c>
       <c r="AF142" t="inlineStr"/>
+      <c r="AG142" t="inlineStr"/>
+      <c r="AH142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -13985,7 +14325,7 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>916471466</v>
+        <v>674782748</v>
       </c>
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr"/>
@@ -14025,6 +14365,8 @@
         </is>
       </c>
       <c r="AF143" t="inlineStr"/>
+      <c r="AG143" t="inlineStr"/>
+      <c r="AH143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -14109,6 +14451,8 @@
         </is>
       </c>
       <c r="AF144" t="inlineStr"/>
+      <c r="AG144" t="inlineStr"/>
+      <c r="AH144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -14193,6 +14537,8 @@
         </is>
       </c>
       <c r="AF145" t="inlineStr"/>
+      <c r="AG145" t="inlineStr"/>
+      <c r="AH145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -14277,6 +14623,8 @@
         </is>
       </c>
       <c r="AF146" t="inlineStr"/>
+      <c r="AG146" t="inlineStr"/>
+      <c r="AH146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -14361,6 +14709,8 @@
         </is>
       </c>
       <c r="AF147" t="inlineStr"/>
+      <c r="AG147" t="inlineStr"/>
+      <c r="AH147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -14445,6 +14795,8 @@
         </is>
       </c>
       <c r="AF148" t="inlineStr"/>
+      <c r="AG148" t="inlineStr"/>
+      <c r="AH148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -14529,6 +14881,8 @@
         </is>
       </c>
       <c r="AF149" t="inlineStr"/>
+      <c r="AG149" t="inlineStr"/>
+      <c r="AH149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -14613,6 +14967,8 @@
         </is>
       </c>
       <c r="AF150" t="inlineStr"/>
+      <c r="AG150" t="inlineStr"/>
+      <c r="AH150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -14697,6 +15053,8 @@
         </is>
       </c>
       <c r="AF151" t="inlineStr"/>
+      <c r="AG151" t="inlineStr"/>
+      <c r="AH151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -14781,6 +15139,8 @@
         </is>
       </c>
       <c r="AF152" t="inlineStr"/>
+      <c r="AG152" t="inlineStr"/>
+      <c r="AH152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -14865,6 +15225,8 @@
         </is>
       </c>
       <c r="AF153" t="inlineStr"/>
+      <c r="AG153" t="inlineStr"/>
+      <c r="AH153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -14909,7 +15271,7 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>557968416</v>
+        <v>819487316</v>
       </c>
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr"/>
@@ -14949,6 +15311,8 @@
         </is>
       </c>
       <c r="AF154" t="inlineStr"/>
+      <c r="AG154" t="inlineStr"/>
+      <c r="AH154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -15033,6 +15397,8 @@
         </is>
       </c>
       <c r="AF155" t="inlineStr"/>
+      <c r="AG155" t="inlineStr"/>
+      <c r="AH155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -15077,7 +15443,7 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>302891595</v>
+        <v>442144888</v>
       </c>
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr"/>
@@ -15117,6 +15483,8 @@
         </is>
       </c>
       <c r="AF156" t="inlineStr"/>
+      <c r="AG156" t="inlineStr"/>
+      <c r="AH156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -15201,6 +15569,8 @@
         </is>
       </c>
       <c r="AF157" t="inlineStr"/>
+      <c r="AG157" t="inlineStr"/>
+      <c r="AH157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -15285,6 +15655,8 @@
         </is>
       </c>
       <c r="AF158" t="inlineStr"/>
+      <c r="AG158" t="inlineStr"/>
+      <c r="AH158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -15369,6 +15741,8 @@
         </is>
       </c>
       <c r="AF159" t="inlineStr"/>
+      <c r="AG159" t="inlineStr"/>
+      <c r="AH159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -15453,6 +15827,8 @@
         </is>
       </c>
       <c r="AF160" t="inlineStr"/>
+      <c r="AG160" t="inlineStr"/>
+      <c r="AH160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -15537,6 +15913,8 @@
         </is>
       </c>
       <c r="AF161" t="inlineStr"/>
+      <c r="AG161" t="inlineStr"/>
+      <c r="AH161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -15621,6 +15999,8 @@
         </is>
       </c>
       <c r="AF162" t="inlineStr"/>
+      <c r="AG162" t="inlineStr"/>
+      <c r="AH162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -15648,7 +16028,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Brittany's</t>
+          <t>Hallmark Jewelers</t>
         </is>
       </c>
       <c r="G163" t="inlineStr"/>
@@ -15678,7 +16058,7 @@
         </is>
       </c>
       <c r="U163" t="n">
-        <v>12500</v>
+        <v>1800</v>
       </c>
       <c r="V163" t="inlineStr"/>
       <c r="W163" t="inlineStr"/>
@@ -15705,6 +16085,8 @@
         </is>
       </c>
       <c r="AF163" t="inlineStr"/>
+      <c r="AG163" t="inlineStr"/>
+      <c r="AH163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -15732,7 +16114,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Brittany's</t>
+          <t>Thornwood Appliance Co.</t>
         </is>
       </c>
       <c r="G164" t="inlineStr"/>
@@ -15741,15 +16123,15 @@
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="n">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Clothing, Clothing Accessories, Shoe, and Jewelry Retailers</t>
+          <t>Furniture, Home Furnishings, Electronics, and Appliance Retailers</t>
         </is>
       </c>
       <c r="N164" t="n">
-        <v>718245555</v>
+        <v>646348968</v>
       </c>
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr"/>
@@ -15762,7 +16144,7 @@
         </is>
       </c>
       <c r="U164" t="n">
-        <v>3000</v>
+        <v>2200</v>
       </c>
       <c r="V164" t="inlineStr"/>
       <c r="W164" t="inlineStr"/>
@@ -15789,6 +16171,8 @@
         </is>
       </c>
       <c r="AF164" t="inlineStr"/>
+      <c r="AG164" t="inlineStr"/>
+      <c r="AH164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -15816,7 +16200,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Brittany's</t>
+          <t>Ridgeline Lumber &amp; Supply</t>
         </is>
       </c>
       <c r="G165" t="inlineStr"/>
@@ -15825,11 +16209,11 @@
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="n">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Clothing, Clothing Accessories, Shoe, and Jewelry Retailers</t>
+          <t>Building Material and Garden Equipment and Supplies Dealers</t>
         </is>
       </c>
       <c r="N165" t="n">
@@ -15846,7 +16230,7 @@
         </is>
       </c>
       <c r="U165" t="n">
-        <v>2500</v>
+        <v>650</v>
       </c>
       <c r="V165" t="inlineStr"/>
       <c r="W165" t="inlineStr"/>
@@ -15873,6 +16257,8 @@
         </is>
       </c>
       <c r="AF165" t="inlineStr"/>
+      <c r="AG165" t="inlineStr"/>
+      <c r="AH165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -15900,7 +16286,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Brittany's</t>
+          <t>Cascade Furniture Gallery</t>
         </is>
       </c>
       <c r="G166" t="inlineStr"/>
@@ -15909,11 +16295,11 @@
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="n">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Clothing, Clothing Accessories, Shoe, and Jewelry Retailers</t>
+          <t>Furniture, Home Furnishings, Electronics, and Appliance Retailers</t>
         </is>
       </c>
       <c r="N166" t="n">
@@ -15930,7 +16316,7 @@
         </is>
       </c>
       <c r="U166" t="n">
-        <v>30000</v>
+        <v>4500</v>
       </c>
       <c r="V166" t="inlineStr"/>
       <c r="W166" t="inlineStr"/>
@@ -15957,6 +16343,8 @@
         </is>
       </c>
       <c r="AF166" t="inlineStr"/>
+      <c r="AG166" t="inlineStr"/>
+      <c r="AH166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -15984,7 +16372,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Brittany's</t>
+          <t>Meridian Electronics</t>
         </is>
       </c>
       <c r="G167" t="inlineStr"/>
@@ -15993,11 +16381,11 @@
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="n">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Clothing, Clothing Accessories, Shoe, and Jewelry Retailers</t>
+          <t>Furniture, Home Furnishings, Electronics, and Appliance Retailers</t>
         </is>
       </c>
       <c r="N167" t="n">
@@ -16014,7 +16402,7 @@
         </is>
       </c>
       <c r="U167" t="n">
-        <v>25000</v>
+        <v>900</v>
       </c>
       <c r="V167" t="inlineStr"/>
       <c r="W167" t="inlineStr"/>
@@ -16041,6 +16429,8 @@
         </is>
       </c>
       <c r="AF167" t="inlineStr"/>
+      <c r="AG167" t="inlineStr"/>
+      <c r="AH167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -16085,7 +16475,7 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>266506100</v>
+        <v>516182934</v>
       </c>
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr"/>
@@ -16125,6 +16515,8 @@
         </is>
       </c>
       <c r="AF168" t="inlineStr"/>
+      <c r="AG168" t="inlineStr"/>
+      <c r="AH168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -16209,6 +16601,8 @@
         </is>
       </c>
       <c r="AF169" t="inlineStr"/>
+      <c r="AG169" t="inlineStr"/>
+      <c r="AH169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -16293,6 +16687,8 @@
         </is>
       </c>
       <c r="AF170" t="inlineStr"/>
+      <c r="AG170" t="inlineStr"/>
+      <c r="AH170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -16377,6 +16773,8 @@
         </is>
       </c>
       <c r="AF171" t="inlineStr"/>
+      <c r="AG171" t="inlineStr"/>
+      <c r="AH171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -16461,6 +16859,8 @@
         </is>
       </c>
       <c r="AF172" t="inlineStr"/>
+      <c r="AG172" t="inlineStr"/>
+      <c r="AH172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -16505,7 +16905,7 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>749820666</v>
+        <v>204606845</v>
       </c>
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr"/>
@@ -16545,6 +16945,8 @@
         </is>
       </c>
       <c r="AF173" t="inlineStr"/>
+      <c r="AG173" t="inlineStr"/>
+      <c r="AH173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -16629,6 +17031,8 @@
         </is>
       </c>
       <c r="AF174" t="inlineStr"/>
+      <c r="AG174" t="inlineStr"/>
+      <c r="AH174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -16713,6 +17117,8 @@
         </is>
       </c>
       <c r="AF175" t="inlineStr"/>
+      <c r="AG175" t="inlineStr"/>
+      <c r="AH175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -16797,6 +17203,8 @@
         </is>
       </c>
       <c r="AF176" t="inlineStr"/>
+      <c r="AG176" t="inlineStr"/>
+      <c r="AH176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -16881,6 +17289,8 @@
         </is>
       </c>
       <c r="AF177" t="inlineStr"/>
+      <c r="AG177" t="inlineStr"/>
+      <c r="AH177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -16965,6 +17375,8 @@
         </is>
       </c>
       <c r="AF178" t="inlineStr"/>
+      <c r="AG178" t="inlineStr"/>
+      <c r="AH178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -17049,6 +17461,8 @@
         </is>
       </c>
       <c r="AF179" t="inlineStr"/>
+      <c r="AG179" t="inlineStr"/>
+      <c r="AH179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -17133,6 +17547,8 @@
         </is>
       </c>
       <c r="AF180" t="inlineStr"/>
+      <c r="AG180" t="inlineStr"/>
+      <c r="AH180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -17217,6 +17633,8 @@
         </is>
       </c>
       <c r="AF181" t="inlineStr"/>
+      <c r="AG181" t="inlineStr"/>
+      <c r="AH181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -17301,6 +17719,8 @@
         </is>
       </c>
       <c r="AF182" t="inlineStr"/>
+      <c r="AG182" t="inlineStr"/>
+      <c r="AH182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -17385,6 +17805,8 @@
         </is>
       </c>
       <c r="AF183" t="inlineStr"/>
+      <c r="AG183" t="inlineStr"/>
+      <c r="AH183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -17469,6 +17891,8 @@
         </is>
       </c>
       <c r="AF184" t="inlineStr"/>
+      <c r="AG184" t="inlineStr"/>
+      <c r="AH184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -17553,6 +17977,8 @@
         </is>
       </c>
       <c r="AF185" t="inlineStr"/>
+      <c r="AG185" t="inlineStr"/>
+      <c r="AH185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -17637,6 +18063,8 @@
         </is>
       </c>
       <c r="AF186" t="inlineStr"/>
+      <c r="AG186" t="inlineStr"/>
+      <c r="AH186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -17721,6 +18149,8 @@
         </is>
       </c>
       <c r="AF187" t="inlineStr"/>
+      <c r="AG187" t="inlineStr"/>
+      <c r="AH187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -17805,6 +18235,8 @@
         </is>
       </c>
       <c r="AF188" t="inlineStr"/>
+      <c r="AG188" t="inlineStr"/>
+      <c r="AH188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -17889,6 +18321,8 @@
         </is>
       </c>
       <c r="AF189" t="inlineStr"/>
+      <c r="AG189" t="inlineStr"/>
+      <c r="AH189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -17973,6 +18407,8 @@
         </is>
       </c>
       <c r="AF190" t="inlineStr"/>
+      <c r="AG190" t="inlineStr"/>
+      <c r="AH190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -18057,6 +18493,8 @@
         </is>
       </c>
       <c r="AF191" t="inlineStr"/>
+      <c r="AG191" t="inlineStr"/>
+      <c r="AH191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -18141,6 +18579,8 @@
         </is>
       </c>
       <c r="AF192" t="inlineStr"/>
+      <c r="AG192" t="inlineStr"/>
+      <c r="AH192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -18225,6 +18665,8 @@
         </is>
       </c>
       <c r="AF193" t="inlineStr"/>
+      <c r="AG193" t="inlineStr"/>
+      <c r="AH193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -18309,6 +18751,8 @@
         </is>
       </c>
       <c r="AF194" t="inlineStr"/>
+      <c r="AG194" t="inlineStr"/>
+      <c r="AH194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -18393,6 +18837,8 @@
         </is>
       </c>
       <c r="AF195" t="inlineStr"/>
+      <c r="AG195" t="inlineStr"/>
+      <c r="AH195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -18477,6 +18923,8 @@
         </is>
       </c>
       <c r="AF196" t="inlineStr"/>
+      <c r="AG196" t="inlineStr"/>
+      <c r="AH196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -18561,6 +19009,8 @@
         </is>
       </c>
       <c r="AF197" t="inlineStr"/>
+      <c r="AG197" t="inlineStr"/>
+      <c r="AH197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -18645,6 +19095,8 @@
         </is>
       </c>
       <c r="AF198" t="inlineStr"/>
+      <c r="AG198" t="inlineStr"/>
+      <c r="AH198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -18757,6 +19209,12 @@
         </is>
       </c>
       <c r="AF199" t="inlineStr"/>
+      <c r="AG199" t="inlineStr"/>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>Retail Store Owner</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -18865,6 +19323,12 @@
         </is>
       </c>
       <c r="AF200" t="inlineStr"/>
+      <c r="AG200" t="inlineStr"/>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>Restaurant Owner</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -18977,6 +19441,12 @@
         </is>
       </c>
       <c r="AF201" t="inlineStr"/>
+      <c r="AG201" t="inlineStr"/>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>Retail Store Owner</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -19089,6 +19559,12 @@
         </is>
       </c>
       <c r="AF202" t="inlineStr"/>
+      <c r="AG202" t="inlineStr"/>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>Delivery Service Owner</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -19201,6 +19677,12 @@
         </is>
       </c>
       <c r="AF203" t="inlineStr"/>
+      <c r="AG203" t="inlineStr"/>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>Veterinarian</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -19309,6 +19791,12 @@
         </is>
       </c>
       <c r="AF204" t="inlineStr"/>
+      <c r="AG204" t="inlineStr"/>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>Retired</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -19421,6 +19909,12 @@
         </is>
       </c>
       <c r="AF205" t="inlineStr"/>
+      <c r="AG205" t="inlineStr"/>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>Production Line Worker</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -19529,6 +20023,12 @@
         </is>
       </c>
       <c r="AF206" t="inlineStr"/>
+      <c r="AG206" t="inlineStr"/>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>Bar Owner</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -19641,6 +20141,12 @@
         </is>
       </c>
       <c r="AF207" t="inlineStr"/>
+      <c r="AG207" t="inlineStr"/>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>Quality Control Inspector</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -19749,6 +20255,12 @@
         </is>
       </c>
       <c r="AF208" t="inlineStr"/>
+      <c r="AG208" t="inlineStr"/>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>Restaurant Owner</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -19819,6 +20331,8 @@
         </is>
       </c>
       <c r="AF209" t="inlineStr"/>
+      <c r="AG209" t="inlineStr"/>
+      <c r="AH209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -19889,6 +20403,8 @@
         </is>
       </c>
       <c r="AF210" t="inlineStr"/>
+      <c r="AG210" t="inlineStr"/>
+      <c r="AH210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -19959,6 +20475,8 @@
         </is>
       </c>
       <c r="AF211" t="inlineStr"/>
+      <c r="AG211" t="inlineStr"/>
+      <c r="AH211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -20029,6 +20547,8 @@
         </is>
       </c>
       <c r="AF212" t="inlineStr"/>
+      <c r="AG212" t="inlineStr"/>
+      <c r="AH212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -20099,6 +20619,8 @@
         </is>
       </c>
       <c r="AF213" t="inlineStr"/>
+      <c r="AG213" t="inlineStr"/>
+      <c r="AH213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -20169,6 +20691,8 @@
         </is>
       </c>
       <c r="AF214" t="inlineStr"/>
+      <c r="AG214" t="inlineStr"/>
+      <c r="AH214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -20239,6 +20763,8 @@
         </is>
       </c>
       <c r="AF215" t="inlineStr"/>
+      <c r="AG215" t="inlineStr"/>
+      <c r="AH215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -20309,6 +20835,8 @@
         </is>
       </c>
       <c r="AF216" t="inlineStr"/>
+      <c r="AG216" t="inlineStr"/>
+      <c r="AH216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -20379,6 +20907,8 @@
         </is>
       </c>
       <c r="AF217" t="inlineStr"/>
+      <c r="AG217" t="inlineStr"/>
+      <c r="AH217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -20449,6 +20979,8 @@
         </is>
       </c>
       <c r="AF218" t="inlineStr"/>
+      <c r="AG218" t="inlineStr"/>
+      <c r="AH218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -20519,6 +21051,8 @@
         </is>
       </c>
       <c r="AF219" t="inlineStr"/>
+      <c r="AG219" t="inlineStr"/>
+      <c r="AH219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -20589,6 +21123,8 @@
         </is>
       </c>
       <c r="AF220" t="inlineStr"/>
+      <c r="AG220" t="inlineStr"/>
+      <c r="AH220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -20659,6 +21195,8 @@
         </is>
       </c>
       <c r="AF221" t="inlineStr"/>
+      <c r="AG221" t="inlineStr"/>
+      <c r="AH221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -20729,6 +21267,8 @@
         </is>
       </c>
       <c r="AF222" t="inlineStr"/>
+      <c r="AG222" t="inlineStr"/>
+      <c r="AH222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -20799,6 +21339,8 @@
         </is>
       </c>
       <c r="AF223" t="inlineStr"/>
+      <c r="AG223" t="inlineStr"/>
+      <c r="AH223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -20869,6 +21411,8 @@
         </is>
       </c>
       <c r="AF224" t="inlineStr"/>
+      <c r="AG224" t="inlineStr"/>
+      <c r="AH224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -20939,6 +21483,8 @@
         </is>
       </c>
       <c r="AF225" t="inlineStr"/>
+      <c r="AG225" t="inlineStr"/>
+      <c r="AH225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -21009,6 +21555,8 @@
         </is>
       </c>
       <c r="AF226" t="inlineStr"/>
+      <c r="AG226" t="inlineStr"/>
+      <c r="AH226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -21048,8 +21596,14 @@
       </c>
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr"/>
-      <c r="L227" t="inlineStr"/>
-      <c r="M227" t="inlineStr"/>
+      <c r="L227" t="n">
+        <v>525</v>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>Funds, Trusts, and Other Financial Vehicles</t>
+        </is>
+      </c>
       <c r="N227" t="n">
         <v>4056079101</v>
       </c>
@@ -21078,7 +21632,7 @@
         </is>
       </c>
       <c r="U227" t="n">
-        <v>530.45</v>
+        <v>6962.5</v>
       </c>
       <c r="V227" t="inlineStr"/>
       <c r="W227" t="inlineStr"/>
@@ -21109,8 +21663,10 @@
         </is>
       </c>
       <c r="AF227" t="n">
-        <v>26.07</v>
-      </c>
+        <v>8.98</v>
+      </c>
+      <c r="AG227" t="inlineStr"/>
+      <c r="AH227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -21217,6 +21773,12 @@
         </is>
       </c>
       <c r="AF228" t="inlineStr"/>
+      <c r="AG228" t="inlineStr"/>
+      <c r="AH228" t="inlineStr">
+        <is>
+          <t>Delivery Service Owner</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -21319,6 +21881,12 @@
         </is>
       </c>
       <c r="AF229" t="inlineStr"/>
+      <c r="AG229" t="inlineStr"/>
+      <c r="AH229" t="inlineStr">
+        <is>
+          <t>Restaurant Owner</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -21421,6 +21989,12 @@
         </is>
       </c>
       <c r="AF230" t="inlineStr"/>
+      <c r="AG230" t="inlineStr"/>
+      <c r="AH230" t="inlineStr">
+        <is>
+          <t>Restaurant Owner</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -21527,6 +22101,12 @@
         </is>
       </c>
       <c r="AF231" t="inlineStr"/>
+      <c r="AG231" t="inlineStr"/>
+      <c r="AH231" t="inlineStr">
+        <is>
+          <t>Delivery Driver</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -21566,8 +22146,14 @@
       </c>
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr"/>
-      <c r="L232" t="inlineStr"/>
-      <c r="M232" t="inlineStr"/>
+      <c r="L232" t="n">
+        <v>424</v>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>Merchant Wholesalers, Nondurable Goods</t>
+        </is>
+      </c>
       <c r="N232" t="n">
         <v>4056079106</v>
       </c>
@@ -21596,7 +22182,7 @@
         </is>
       </c>
       <c r="U232" t="n">
-        <v>2947.99</v>
+        <v>340999.55</v>
       </c>
       <c r="V232" t="inlineStr"/>
       <c r="W232" t="inlineStr"/>
@@ -21627,8 +22213,10 @@
         </is>
       </c>
       <c r="AF232" t="n">
-        <v>46.98</v>
-      </c>
+        <v>1.96</v>
+      </c>
+      <c r="AG232" t="inlineStr"/>
+      <c r="AH232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -21735,6 +22323,12 @@
         </is>
       </c>
       <c r="AF233" t="inlineStr"/>
+      <c r="AG233" t="inlineStr"/>
+      <c r="AH233" t="inlineStr">
+        <is>
+          <t>Warehouse Associate</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -21837,6 +22431,12 @@
         </is>
       </c>
       <c r="AF234" t="inlineStr"/>
+      <c r="AG234" t="inlineStr"/>
+      <c r="AH234" t="inlineStr">
+        <is>
+          <t>Restaurant Owner</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -21876,8 +22476,14 @@
       </c>
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr"/>
-      <c r="M235" t="inlineStr"/>
+      <c r="L235" t="n">
+        <v>722</v>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>Food Services and Drinking Places</t>
+        </is>
+      </c>
       <c r="N235" t="n">
         <v>4056079109</v>
       </c>
@@ -21906,7 +22512,7 @@
         </is>
       </c>
       <c r="U235" t="n">
-        <v>1379.62</v>
+        <v>64.28</v>
       </c>
       <c r="V235" t="inlineStr"/>
       <c r="W235" t="inlineStr"/>
@@ -21937,8 +22543,14 @@
         </is>
       </c>
       <c r="AF235" t="n">
-        <v>24.58</v>
-      </c>
+        <v>777.91</v>
+      </c>
+      <c r="AG235" t="inlineStr">
+        <is>
+          <t>PERS1008:100</t>
+        </is>
+      </c>
+      <c r="AH235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -21978,8 +22590,14 @@
       </c>
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr"/>
-      <c r="M236" t="inlineStr"/>
+      <c r="L236" t="n">
+        <v>722</v>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>Food Services and Drinking Places</t>
+        </is>
+      </c>
       <c r="N236" t="n">
         <v>4056079110</v>
       </c>
@@ -21994,7 +22612,7 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>4</v>
+        <v>1.25</v>
       </c>
       <c r="R236" t="inlineStr"/>
       <c r="S236" t="inlineStr">
@@ -22008,7 +22626,7 @@
         </is>
       </c>
       <c r="U236" t="n">
-        <v>5818.62</v>
+        <v>64.28</v>
       </c>
       <c r="V236" t="inlineStr"/>
       <c r="W236" t="inlineStr"/>
@@ -22039,8 +22657,14 @@
         </is>
       </c>
       <c r="AF236" t="n">
-        <v>68.77</v>
-      </c>
+        <v>972.38</v>
+      </c>
+      <c r="AG236" t="inlineStr">
+        <is>
+          <t>PERS1010:50,PERS1012:50</t>
+        </is>
+      </c>
+      <c r="AH236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -22143,6 +22767,12 @@
         </is>
       </c>
       <c r="AF237" t="inlineStr"/>
+      <c r="AG237" t="inlineStr"/>
+      <c r="AH237" t="inlineStr">
+        <is>
+          <t>Retired</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -22182,8 +22812,14 @@
       </c>
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr"/>
-      <c r="M238" t="inlineStr"/>
+      <c r="L238" t="n">
+        <v>722</v>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>Food Services and Drinking Places</t>
+        </is>
+      </c>
       <c r="N238" t="n">
         <v>4056079112</v>
       </c>
@@ -22212,7 +22848,7 @@
         </is>
       </c>
       <c r="U238" t="n">
-        <v>470.85</v>
+        <v>64.28</v>
       </c>
       <c r="V238" t="inlineStr"/>
       <c r="W238" t="inlineStr"/>
@@ -22243,8 +22879,14 @@
         </is>
       </c>
       <c r="AF238" t="n">
-        <v>39.59</v>
-      </c>
+        <v>388.95</v>
+      </c>
+      <c r="AG238" t="inlineStr">
+        <is>
+          <t>PERS1013:100</t>
+        </is>
+      </c>
+      <c r="AH238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -22351,6 +22993,12 @@
         </is>
       </c>
       <c r="AF239" t="inlineStr"/>
+      <c r="AG239" t="inlineStr"/>
+      <c r="AH239" t="inlineStr">
+        <is>
+          <t>Retail Store Owner</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -22390,8 +23038,14 @@
       </c>
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr"/>
-      <c r="L240" t="inlineStr"/>
-      <c r="M240" t="inlineStr"/>
+      <c r="L240" t="n">
+        <v>424</v>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>Merchant Wholesalers, Nondurable Goods</t>
+        </is>
+      </c>
       <c r="N240" t="n">
         <v>4056079114</v>
       </c>
@@ -22420,7 +23074,7 @@
         </is>
       </c>
       <c r="U240" t="n">
-        <v>556.04</v>
+        <v>5537.5</v>
       </c>
       <c r="V240" t="inlineStr"/>
       <c r="W240" t="inlineStr"/>
@@ -22451,8 +23105,10 @@
         </is>
       </c>
       <c r="AF240" t="n">
-        <v>26.24</v>
-      </c>
+        <v>22.57</v>
+      </c>
+      <c r="AG240" t="inlineStr"/>
+      <c r="AH240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -22492,8 +23148,14 @@
       </c>
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr"/>
-      <c r="L241" t="inlineStr"/>
-      <c r="M241" t="inlineStr"/>
+      <c r="L241" t="n">
+        <v>423</v>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>Merchant Wholesalers, Durable Goods</t>
+        </is>
+      </c>
       <c r="N241" t="n">
         <v>4056079115</v>
       </c>
@@ -22522,7 +23184,7 @@
         </is>
       </c>
       <c r="U241" t="n">
-        <v>501.98</v>
+        <v>56937.5</v>
       </c>
       <c r="V241" t="inlineStr"/>
       <c r="W241" t="inlineStr"/>
@@ -22553,8 +23215,10 @@
         </is>
       </c>
       <c r="AF241" t="n">
-        <v>40</v>
-      </c>
+        <v>5.85</v>
+      </c>
+      <c r="AG241" t="inlineStr"/>
+      <c r="AH241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -22661,6 +23325,12 @@
         </is>
       </c>
       <c r="AF242" t="inlineStr"/>
+      <c r="AG242" t="inlineStr"/>
+      <c r="AH242" t="inlineStr">
+        <is>
+          <t>Machine Operator</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -22700,8 +23370,14 @@
       </c>
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr"/>
-      <c r="L243" t="inlineStr"/>
-      <c r="M243" t="inlineStr"/>
+      <c r="L243" t="n">
+        <v>722</v>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>Food Services and Drinking Places</t>
+        </is>
+      </c>
       <c r="N243" t="n">
         <v>4056079117</v>
       </c>
@@ -22730,7 +23406,7 @@
         </is>
       </c>
       <c r="U243" t="n">
-        <v>815.42</v>
+        <v>64.28</v>
       </c>
       <c r="V243" t="inlineStr"/>
       <c r="W243" t="inlineStr"/>
@@ -22761,8 +23437,14 @@
         </is>
       </c>
       <c r="AF243" t="n">
-        <v>35.91</v>
-      </c>
+        <v>1166.86</v>
+      </c>
+      <c r="AG243" t="inlineStr">
+        <is>
+          <t>PERS1016:100</t>
+        </is>
+      </c>
+      <c r="AH243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -22869,6 +23551,12 @@
         </is>
       </c>
       <c r="AF244" t="inlineStr"/>
+      <c r="AG244" t="inlineStr"/>
+      <c r="AH244" t="inlineStr">
+        <is>
+          <t>Retail Store Owner</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -22908,8 +23596,14 @@
       </c>
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr"/>
-      <c r="L245" t="inlineStr"/>
-      <c r="M245" t="inlineStr"/>
+      <c r="L245" t="n">
+        <v>722</v>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>Food Services and Drinking Places</t>
+        </is>
+      </c>
       <c r="N245" t="n">
         <v>4056079119</v>
       </c>
@@ -22938,7 +23632,7 @@
         </is>
       </c>
       <c r="U245" t="n">
-        <v>430.41</v>
+        <v>64.28</v>
       </c>
       <c r="V245" t="inlineStr"/>
       <c r="W245" t="inlineStr"/>
@@ -22969,8 +23663,14 @@
         </is>
       </c>
       <c r="AF245" t="n">
-        <v>20.35</v>
-      </c>
+        <v>583.4299999999999</v>
+      </c>
+      <c r="AG245" t="inlineStr">
+        <is>
+          <t>PERS1006:60,PERS1017:40</t>
+        </is>
+      </c>
+      <c r="AH245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -23077,6 +23777,12 @@
         </is>
       </c>
       <c r="AF246" t="inlineStr"/>
+      <c r="AG246" t="inlineStr"/>
+      <c r="AH246" t="inlineStr">
+        <is>
+          <t>Production Supervisor</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -23116,8 +23822,14 @@
       </c>
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr"/>
-      <c r="L247" t="inlineStr"/>
-      <c r="M247" t="inlineStr"/>
+      <c r="L247" t="n">
+        <v>523</v>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>Securities, Commodity Contracts, and Other Financial Investments and Related Activities</t>
+        </is>
+      </c>
       <c r="N247" t="n">
         <v>4056079121</v>
       </c>
@@ -23146,7 +23858,7 @@
         </is>
       </c>
       <c r="U247" t="n">
-        <v>548.1799999999999</v>
+        <v>50462.5</v>
       </c>
       <c r="V247" t="inlineStr"/>
       <c r="W247" t="inlineStr"/>
@@ -23177,8 +23889,10 @@
         </is>
       </c>
       <c r="AF247" t="n">
-        <v>33.91</v>
-      </c>
+        <v>2.48</v>
+      </c>
+      <c r="AG247" t="inlineStr"/>
+      <c r="AH247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -23285,6 +23999,12 @@
         </is>
       </c>
       <c r="AF248" t="inlineStr"/>
+      <c r="AG248" t="inlineStr"/>
+      <c r="AH248" t="inlineStr">
+        <is>
+          <t>Plant Maintenance Technician</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -23324,8 +24044,14 @@
       </c>
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr"/>
+      <c r="L249" t="n">
+        <v>722</v>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>Food Services and Drinking Places</t>
+        </is>
+      </c>
       <c r="N249" t="n">
         <v>4056079123</v>
       </c>
@@ -23354,7 +24080,7 @@
         </is>
       </c>
       <c r="U249" t="n">
-        <v>636.84</v>
+        <v>64.28</v>
       </c>
       <c r="V249" t="inlineStr"/>
       <c r="W249" t="inlineStr"/>
@@ -23385,8 +24111,14 @@
         </is>
       </c>
       <c r="AF249" t="n">
-        <v>20.51</v>
-      </c>
+        <v>388.95</v>
+      </c>
+      <c r="AG249" t="inlineStr">
+        <is>
+          <t>PERS1021:100</t>
+        </is>
+      </c>
+      <c r="AH249" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
